--- a/resultados/memoria.xlsx
+++ b/resultados/memoria.xlsx
@@ -225,7 +225,7 @@
     <t xml:space="preserve">FreshFinder - cartera</t>
   </si>
   <si>
-    <t xml:space="preserve">Pausado</t>
+    <t xml:space="preserve">En pausa</t>
   </si>
   <si>
     <t xml:space="preserve">Pinza - Pruebas</t>
@@ -2786,7 +2786,7 @@
       </c>
       <c r="B4" s="4" t="str">
         <f aca="false">IFERROR(INDEX(Seguimiento!$E:$E,MATCH(X4&amp;"#"&amp;_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$R:$R,X4),Seguimiento!$S:$S,0)),"Activado")</f>
-        <v>Pausado</v>
+        <v>En pausa</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>95</v>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="B5" s="4" t="str">
         <f aca="false">IFERROR(INDEX(Seguimiento!$E:$E,MATCH(X5&amp;"#"&amp;_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$R:$R,X5),Seguimiento!$S:$S,0)),"Activado")</f>
-        <v>Pausado</v>
+        <v>En pausa</v>
       </c>
       <c r="C5" s="13" t="s">
         <v>99</v>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="B6" s="4" t="str">
         <f aca="false">IFERROR(INDEX(Seguimiento!$E:$E,MATCH(X6&amp;"#"&amp;_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$R:$R,X6),Seguimiento!$S:$S,0)),"Activado")</f>
-        <v>Pausado</v>
+        <v>En pausa</v>
       </c>
       <c r="C6" s="13" t="s">
         <v>102</v>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="B7" s="4" t="str">
         <f aca="false">IFERROR(INDEX(Seguimiento!$E:$E,MATCH(X7&amp;"#"&amp;_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$R:$R,X7),Seguimiento!$S:$S,0)),"Activado")</f>
-        <v>Pausado</v>
+        <v>En pausa</v>
       </c>
       <c r="C7" s="13" t="s">
         <v>102</v>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="B8" s="4" t="str">
         <f aca="false">IFERROR(INDEX(Seguimiento!$E:$E,MATCH(X8&amp;"#"&amp;_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$R:$R,X8),Seguimiento!$S:$S,0)),"Activado")</f>
-        <v>Pausado</v>
+        <v>En pausa</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>95</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="B9" s="4" t="str">
         <f aca="false">IFERROR(INDEX(Seguimiento!$E:$E,MATCH(X9&amp;"#"&amp;_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$R:$R,X9),Seguimiento!$S:$S,0)),"Activado")</f>
-        <v>Pausado</v>
+        <v>En pausa</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>107</v>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="B10" s="4" t="str">
         <f aca="false">IFERROR(INDEX(Seguimiento!$E:$E,MATCH(X10&amp;"#"&amp;_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$R:$R,X10),Seguimiento!$S:$S,0)),"Activado")</f>
-        <v>Pausado</v>
+        <v>En pausa</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>110</v>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="B11" s="4" t="str">
         <f aca="false">IFERROR(INDEX(Seguimiento!$E:$E,MATCH(X11&amp;"#"&amp;_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$R:$R,X11),Seguimiento!$S:$S,0)),"Activado")</f>
-        <v>Pausado</v>
+        <v>En pausa</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>112</v>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="B12" s="4" t="str">
         <f aca="false">IFERROR(INDEX(Seguimiento!$E:$E,MATCH(X12&amp;"#"&amp;_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$R:$R,X12),Seguimiento!$S:$S,0)),"Activado")</f>
-        <v>Pausado</v>
+        <v>En pausa</v>
       </c>
       <c r="C12" s="14" t="s">
         <v>114</v>
@@ -3605,7 +3605,7 @@
       </c>
       <c r="B13" s="4" t="str">
         <f aca="false">IFERROR(INDEX(Seguimiento!$E:$E,MATCH(X13&amp;"#"&amp;_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$R:$R,X13),Seguimiento!$S:$S,0)),"Activado")</f>
-        <v>Pausado</v>
+        <v>En pausa</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>116</v>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="B14" s="4" t="str">
         <f aca="false">IFERROR(INDEX(Seguimiento!$E:$E,MATCH(X14&amp;"#"&amp;_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$R:$R,X14),Seguimiento!$S:$S,0)),"Activado")</f>
-        <v>Pausado</v>
+        <v>En pausa</v>
       </c>
       <c r="C14" s="15" t="s">
         <v>118</v>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="B15" s="4" t="str">
         <f aca="false">IFERROR(INDEX(Seguimiento!$E:$E,MATCH(X15&amp;"#"&amp;_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$R:$R,X15),Seguimiento!$S:$S,0)),"Activado")</f>
-        <v>Pausado</v>
+        <v>En pausa</v>
       </c>
       <c r="C15" s="15" t="s">
         <v>122</v>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="B16" s="4" t="str">
         <f aca="false">IFERROR(INDEX(Seguimiento!$E:$E,MATCH(X16&amp;"#"&amp;_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$R:$R,X16),Seguimiento!$S:$S,0)),"Activado")</f>
-        <v>Pausado</v>
+        <v>En pausa</v>
       </c>
       <c r="C16" s="15" t="s">
         <v>124</v>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="B17" s="4" t="str">
         <f aca="false">IFERROR(INDEX(Seguimiento!$E:$E,MATCH(X17&amp;"#"&amp;_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$R:$R,X17),Seguimiento!$S:$S,0)),"Activado")</f>
-        <v>Pausado</v>
+        <v>En pausa</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>126</v>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="B18" s="4" t="str">
         <f aca="false">IFERROR(INDEX(Seguimiento!$E:$E,MATCH(X18&amp;"#"&amp;_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$R:$R,X18),Seguimiento!$S:$S,0)),"Activado")</f>
-        <v>Pausado</v>
+        <v>En pausa</v>
       </c>
       <c r="C18" s="15" t="s">
         <v>128</v>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="B19" s="4" t="str">
         <f aca="false">IFERROR(INDEX(Seguimiento!$E:$E,MATCH(X19&amp;"#"&amp;_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$R:$R,X19),Seguimiento!$S:$S,0)),"Activado")</f>
-        <v>Pausado</v>
+        <v>En pausa</v>
       </c>
       <c r="C19" s="13" t="s">
         <v>132</v>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="B20" s="4" t="str">
         <f aca="false">IFERROR(INDEX(Seguimiento!$E:$E,MATCH(X20&amp;"#"&amp;_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$R:$R,X20),Seguimiento!$S:$S,0)),"Activado")</f>
-        <v>Pausado</v>
+        <v>En pausa</v>
       </c>
       <c r="C20" s="13" t="s">
         <v>134</v>
@@ -4333,7 +4333,7 @@
       </c>
       <c r="B21" s="4" t="str">
         <f aca="false">IFERROR(INDEX(Seguimiento!$E:$E,MATCH(X21&amp;"#"&amp;_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$R:$R,X21),Seguimiento!$S:$S,0)),"Activado")</f>
-        <v>Pausado</v>
+        <v>En pausa</v>
       </c>
       <c r="C21" s="13" t="s">
         <v>136</v>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="B22" s="4" t="str">
         <f aca="false">IFERROR(INDEX(Seguimiento!$E:$E,MATCH(X22&amp;"#"&amp;_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$R:$R,X22),Seguimiento!$S:$S,0)),"Activado")</f>
-        <v>Pausado</v>
+        <v>En pausa</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>138</v>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="B23" s="4" t="str">
         <f aca="false">IFERROR(INDEX(Seguimiento!$E:$E,MATCH(X23&amp;"#"&amp;_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$R:$R,X23),Seguimiento!$S:$S,0)),"Activado")</f>
-        <v>Pausado</v>
+        <v>En pausa</v>
       </c>
       <c r="C23" s="14" t="s">
         <v>140</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B24" s="4" t="str">
         <f aca="false">IFERROR(INDEX(Seguimiento!$E:$E,MATCH(X24&amp;"#"&amp;_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$R:$R,X24),Seguimiento!$S:$S,0)),"Activado")</f>
-        <v>Pausado</v>
+        <v>En pausa</v>
       </c>
       <c r="C24" s="14" t="s">
         <v>142</v>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="B25" s="4" t="str">
         <f aca="false">IFERROR(INDEX(Seguimiento!$E:$E,MATCH(X25&amp;"#"&amp;_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$R:$R,X25),Seguimiento!$S:$S,0)),"Activado")</f>
-        <v>Pausado</v>
+        <v>En pausa</v>
       </c>
       <c r="C25" s="14" t="s">
         <v>144</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="B26" s="4" t="str">
         <f aca="false">IFERROR(INDEX(Seguimiento!$E:$E,MATCH(X26&amp;"#"&amp;_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$R:$R,X26),Seguimiento!$S:$S,0)),"Activado")</f>
-        <v>Pausado</v>
+        <v>En pausa</v>
       </c>
       <c r="C26" s="14" t="s">
         <v>146</v>
@@ -4879,7 +4879,7 @@
       </c>
       <c r="B27" s="4" t="str">
         <f aca="false">IFERROR(INDEX(Seguimiento!$E:$E,MATCH(X27&amp;"#"&amp;_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$R:$R,X27),Seguimiento!$S:$S,0)),"Activado")</f>
-        <v>Pausado</v>
+        <v>En pausa</v>
       </c>
       <c r="C27" s="14" t="s">
         <v>148</v>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="B28" s="4" t="str">
         <f aca="false">IFERROR(INDEX(Seguimiento!$E:$E,MATCH(X28&amp;"#"&amp;_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$R:$R,X28),Seguimiento!$S:$S,0)),"Activado")</f>
-        <v>Pausado</v>
+        <v>En pausa</v>
       </c>
       <c r="C28" s="14" t="s">
         <v>150</v>
@@ -29313,7 +29313,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E4:E603" type="list">
-      <formula1>"Activado,Pausado,Archivado"</formula1>
+      <formula1>"Activado,En pausa,Archivado"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -31676,7 +31676,7 @@
         <v>Pendiente de aplicar</v>
       </c>
       <c r="Z30" s="36" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="AA30" s="43"/>
     </row>
